--- a/AAII_Financials/Quarterly/ATS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>ATS</t>
   </si>
@@ -656,287 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44927</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44556</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44465</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>488900</v>
+      </c>
+      <c r="E8" s="3">
         <v>535200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>556400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>522400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>539500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>399500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>452400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>454100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>507300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>584500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>569500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>543900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>569100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>540100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>647000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>589000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>610600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>603200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>546800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>522100</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E9" s="3">
         <v>400000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>391100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>365500</v>
       </c>
-      <c r="G9" s="3">
-        <v>378500</v>
-      </c>
       <c r="H9" s="3">
+        <v>377700</v>
+      </c>
+      <c r="I9" s="3">
         <v>355400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>312700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>319200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>354900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>419400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>406000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>388900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>407700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>383600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>462700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>426600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>440600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>429400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>388600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>378400</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>145300</v>
+      </c>
+      <c r="E10" s="3">
         <v>135200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>165400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>157000</v>
       </c>
-      <c r="G10" s="3">
-        <v>161000</v>
-      </c>
       <c r="H10" s="3">
+        <v>161800</v>
+      </c>
+      <c r="I10" s="3">
         <v>44100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>139700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>134900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>152300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>165100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>163500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>155000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>161400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>156500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>184300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>162400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>170000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>173800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>158200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>143700</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,53 +972,54 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>33000</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>27800</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3">
         <v>21600</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,115 +1100,121 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E14" s="3">
         <v>10900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>20300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E15" s="3">
         <v>6600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>454900</v>
+      </c>
+      <c r="E17" s="3">
         <v>518500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>510000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>468400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>495100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>458300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>418900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>423800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>456200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>519500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>496400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>481600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>509400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>489000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>591000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>535900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>549000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>543300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>508600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>478500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E18" s="3">
         <v>16700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>54000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>44400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-58800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>51100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>65000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>73000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>62300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>59800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>51100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>56000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>53100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>61600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>38200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,8 +1409,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1420,274 +1454,289 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>800</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E21" s="3">
         <v>23300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>68600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>75300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>65100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-52800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>53300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>72500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>72000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>94100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>82100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>81300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>57700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>84700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>83200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>95300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>92400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>68200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>18600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-97600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>35100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>49900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>46900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>39600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>50800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>50200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>30400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-49700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-47900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>39400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>39900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-47900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>39200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>40800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,8 +2187,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2164,88 +2234,94 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-800</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-47900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>39200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>40800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>23900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-47900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>39200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>40800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>23900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44927</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44556</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44465</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,70 +2569,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140200</v>
+      </c>
+      <c r="E41" s="3">
         <v>204100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>138100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>157200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>182600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>183000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>135200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>125700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>197500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>138500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>93300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>118200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>302100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>95200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>139900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>135300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>181300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2563,20 +2653,20 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>1800</v>
       </c>
       <c r="J42" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K42" s="3">
         <v>600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2607,301 +2697,316 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>701700</v>
+      </c>
+      <c r="E43" s="3">
         <v>712400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>853500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>838600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>820600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>890200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>949600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>905600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>969600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>892700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>896600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>841600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>784400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>706400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>912100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>946400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>843100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>744800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>751900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>755100</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>214900</v>
+      </c>
+      <c r="E44" s="3">
         <v>211500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>225400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>229900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>227300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>222800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>254100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>253700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>222700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>218500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>236800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>207100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>203600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>189800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>251900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>236500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>225800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>207900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>205600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>144200</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E45" s="3">
         <v>64900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>71300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>71800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>64400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>58500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1152200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1222400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1328100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1282600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1260700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1325600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1439400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1400800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1390300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1295100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1400300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1242900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1138200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1073100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1537400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1349900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1273200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1146500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1205500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1132400</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>800</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>1500</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12300</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -2915,134 +3020,143 @@
         <v>0</v>
       </c>
       <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E48" s="3">
         <v>291500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>320700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>322700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>325500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>311200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>305500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>322800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>296300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>297300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>295900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>280000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>270500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>264100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>322300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>302200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>299700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>303400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>311200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>289700</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1484800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1506900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1538600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1538200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1550300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1498000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1473500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1535700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1394200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1409100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1454000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1242000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1263600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1264900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1673300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1606500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1576300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1593000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1648800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1104200</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,29 +3282,32 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E52" s="3">
         <v>5900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
@@ -3210,25 +3330,28 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>20900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>25500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3019400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3109200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3279300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3227100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3228200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3215600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3237600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3283700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3099600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3019500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3163700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2784700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2688800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2619200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3553900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3290400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3166200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3069400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3190900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2566100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,339 +3529,355 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>369200</v>
+      </c>
+      <c r="E57" s="3">
         <v>365000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>402000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>407500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>383200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>382900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>365600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>432000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>360800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>383900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>404000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>386500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>376700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>406900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>503200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>484900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>520800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>501500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>484900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E58" s="3">
         <v>30200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>30200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>26300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>41900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>23500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>22100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>37800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>23000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>301800</v>
+      </c>
+      <c r="E59" s="3">
         <v>334700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>361000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>336500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>355400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>346400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>346100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>190400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>361200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>327900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>365900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>283500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>268100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>298900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>410300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>382600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>335100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>321800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>385000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>394800</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>705400</v>
+      </c>
+      <c r="E60" s="3">
         <v>743700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>804000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>787000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>780300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>783000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>750000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>672200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>774700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>760100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>825500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>719200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>715700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>771300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>945700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>905300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>877800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>845000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>893000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>854300</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>968100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1013500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1088000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1089600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1109200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1152700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1190900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1273000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1016300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>937700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1000700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>813500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>727400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>916200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1363900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1230500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1145800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1079500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1132800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>583000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3753,26 +3899,29 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>162700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>147200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>154100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>159200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>193200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>138100</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1748700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1834400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1976000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1956900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1976700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2026300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2019200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2033000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1866600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1776000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1938300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1624500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1533800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1783600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2475800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2286600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2181300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2087800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2222500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1593200</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>509100</v>
+      </c>
+      <c r="E72" s="3">
         <v>517700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>540000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>508000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>494000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>459400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>506000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>535700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>528800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>535000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>512200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>465300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>436700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>392200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>497600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>468300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>439100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>416800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>378400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>368900</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1269400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1273600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1301900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1268900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1250100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1186800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1215900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1248100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1230400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1241100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1222900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1157900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1152300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>832800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1078200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1003800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>985000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>981600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>968400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>972900</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44927</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44556</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44465</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-47900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>39200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>40800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>23900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E83" s="3">
         <v>12100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>11600</v>
       </c>
       <c r="H83" s="3">
         <v>11600</v>
       </c>
       <c r="I83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J83" s="3">
         <v>10900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>27900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>33600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>107100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>83800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>114100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-33200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>83700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-81400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>60200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>116100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-38000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-31700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>82100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>55700</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-203900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-43100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>9800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-589500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62600</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5590,8 +5824,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,190 +6037,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-73400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-129600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>223100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>47600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-55700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>176300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>59800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>69800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-115300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>130900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>28000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-90100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>541700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-29800</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-61400</v>
+      </c>
+      <c r="E102" s="3">
         <v>15700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>48100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>45800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-105200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>207000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-44700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-64800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-35100</v>
       </c>
     </row>
